--- a/pensum/ol18/LOM_Ovingsark_OrgLedelse_kap18_Hva_en_feilansettelse_koster_NY.xlsx
+++ b/pensum/ol18/LOM_Ovingsark_OrgLedelse_kap18_Hva_en_feilansettelse_koster_NY.xlsx
@@ -1090,15 +1090,15 @@
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>Produksjonslønn for hele bedriften, ett år</t>
+          <t>Grunnlønn til montører og lærlinger, ett år (før sosiale kostnader)</t>
         </is>
       </c>
       <c r="B5" s="10" t="n">
-        <v>5180000</v>
+        <v>5750000</v>
       </c>
       <c r="D5" s="6" t="inlineStr">
         <is>
-          <t>Lønnsposten i resultatregnskapet for 2026, jf. kapittel 3.</t>
+          <t>Lønnsposten i resultatregnskapet for 2026 (8 440 000 kr, jf. kapittel 3) inkluderer feriepenger og avgifter. Her er grunnlønna: 8 440 000 / 1,468.</t>
         </is>
       </c>
     </row>
